--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-lungenfunktion-provokationstest-messung.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-lungenfunktion-provokationstest-messung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$145</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5067" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5106" uniqueCount="660">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02</t>
+    <t>2026-09-15</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1289,6 +1289,9 @@
     <t>Procedure.code.coding.extension.value[x].code</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Procedure.code.coding:ops.extension:Seitenlokalisation.value[x].display</t>
   </si>
   <si>
@@ -1821,6 +1824,22 @@
   </si>
   <si>
     <t>Procedure.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite}
+</t>
+  </si>
+  <si>
+    <t>Target anatomic location or structure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
   </si>
   <si>
     <t>Procedure.bodySite.coding</t>
@@ -2374,7 +2393,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM144"/>
+  <dimension ref="A1:AM145"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.5703125" customWidth="true" bestFit="true"/>
@@ -4618,7 +4637,7 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>113</v>
@@ -4838,7 +4857,7 @@
         <v>85</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>97</v>
@@ -9272,7 +9291,7 @@
         <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>113</v>
@@ -9603,7 +9622,7 @@
         <v>78</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>113</v>
@@ -9821,7 +9840,7 @@
         <v>85</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>97</v>
@@ -10041,7 +10060,7 @@
         <v>78</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>113</v>
@@ -10154,7 +10173,7 @@
         <v>85</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>97</v>
@@ -10265,7 +10284,7 @@
         <v>85</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>97</v>
@@ -10316,7 +10335,9 @@
       <c r="M72" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="N72" s="2"/>
+      <c r="N72" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="O72" t="s" s="2">
         <v>244</v>
       </c>
@@ -10376,7 +10397,7 @@
         <v>85</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>97</v>
@@ -10393,10 +10414,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10427,7 +10448,9 @@
       <c r="M73" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N73" s="2"/>
+      <c r="N73" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="O73" t="s" s="2">
         <v>251</v>
       </c>
@@ -10487,7 +10510,7 @@
         <v>85</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>97</v>
@@ -10504,10 +10527,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10600,7 +10623,7 @@
         <v>85</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>97</v>
@@ -10617,10 +10640,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10646,7 +10669,7 @@
         <v>126</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>227</v>
@@ -10662,7 +10685,7 @@
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>76</v>
@@ -10713,7 +10736,7 @@
         <v>85</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>97</v>
@@ -10730,10 +10753,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10759,10 +10782,10 @@
         <v>99</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>237</v>
@@ -10824,7 +10847,7 @@
         <v>85</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>97</v>
@@ -10841,10 +10864,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10870,12 +10893,14 @@
         <v>160</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M77" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="N77" s="2"/>
+      <c r="N77" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="O77" t="s" s="2">
         <v>244</v>
       </c>
@@ -10890,7 +10915,7 @@
         <v>76</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>76</v>
@@ -10935,10 +10960,10 @@
         <v>85</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>76</v>
@@ -10952,10 +10977,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10986,7 +11011,9 @@
       <c r="M78" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N78" s="2"/>
+      <c r="N78" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="O78" t="s" s="2">
         <v>251</v>
       </c>
@@ -11046,7 +11073,7 @@
         <v>85</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>97</v>
@@ -11063,10 +11090,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11159,7 +11186,7 @@
         <v>85</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>97</v>
@@ -11176,7 +11203,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>371</v>
@@ -11226,7 +11253,7 @@
         <v>76</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>76</v>
@@ -11245,7 +11272,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>76</v>
@@ -11289,7 +11316,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>380</v>
@@ -11398,7 +11425,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>382</v>
@@ -11509,10 +11536,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11622,10 +11649,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11733,10 +11760,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11844,10 +11871,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11955,10 +11982,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12068,10 +12095,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12181,14 +12208,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12207,13 +12234,13 @@
         <v>86</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12264,7 +12291,7 @@
         <v>76</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>85</v>
@@ -12279,21 +12306,21 @@
         <v>97</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12399,10 +12426,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12510,10 +12537,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12539,13 +12566,13 @@
         <v>99</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12595,7 +12622,7 @@
         <v>76</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
@@ -12604,7 +12631,7 @@
         <v>85</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>97</v>
@@ -12621,10 +12648,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12650,13 +12677,13 @@
         <v>126</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12685,10 +12712,10 @@
         <v>142</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>76</v>
@@ -12706,7 +12733,7 @@
         <v>76</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
@@ -12732,10 +12759,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12761,13 +12788,13 @@
         <v>269</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12817,7 +12844,7 @@
         <v>76</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
@@ -12843,10 +12870,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12872,13 +12899,13 @@
         <v>99</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12928,7 +12955,7 @@
         <v>76</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -12954,10 +12981,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12980,16 +13007,16 @@
         <v>86</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13039,7 +13066,7 @@
         <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
@@ -13054,21 +13081,21 @@
         <v>97</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13174,10 +13201,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13285,10 +13312,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13314,13 +13341,13 @@
         <v>99</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13370,7 +13397,7 @@
         <v>76</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -13379,7 +13406,7 @@
         <v>85</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>97</v>
@@ -13396,10 +13423,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13425,13 +13452,13 @@
         <v>126</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13460,10 +13487,10 @@
         <v>142</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>76</v>
@@ -13481,7 +13508,7 @@
         <v>76</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
@@ -13507,10 +13534,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13536,13 +13563,13 @@
         <v>269</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13592,7 +13619,7 @@
         <v>76</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
@@ -13618,10 +13645,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13647,13 +13674,13 @@
         <v>99</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13703,7 +13730,7 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -13729,10 +13756,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13755,16 +13782,16 @@
         <v>86</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13802,17 +13829,17 @@
         <v>76</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -13827,24 +13854,24 @@
         <v>97</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>76</v>
@@ -13869,13 +13896,13 @@
         <v>204</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13925,7 +13952,7 @@
         <v>76</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
@@ -13940,24 +13967,24 @@
         <v>97</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>76</v>
@@ -13979,16 +14006,16 @@
         <v>86</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14038,7 +14065,7 @@
         <v>76</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
@@ -14053,21 +14080,21 @@
         <v>97</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14090,13 +14117,13 @@
         <v>86</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14147,7 +14174,7 @@
         <v>76</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
@@ -14165,7 +14192,7 @@
         <v>76</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>76</v>
@@ -14173,10 +14200,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14199,13 +14226,13 @@
         <v>86</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14256,7 +14283,7 @@
         <v>76</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
@@ -14274,7 +14301,7 @@
         <v>76</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>76</v>
@@ -14282,10 +14309,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14308,13 +14335,13 @@
         <v>86</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14365,7 +14392,7 @@
         <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
@@ -14380,7 +14407,7 @@
         <v>97</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>76</v>
@@ -14391,10 +14418,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14500,10 +14527,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14611,14 +14638,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -14640,10 +14667,10 @@
         <v>105</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>108</v>
@@ -14698,7 +14725,7 @@
         <v>76</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
@@ -14724,10 +14751,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14753,14 +14780,14 @@
         <v>309</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>76</v>
@@ -14788,10 +14815,10 @@
         <v>150</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>76</v>
@@ -14809,7 +14836,7 @@
         <v>76</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
@@ -14824,21 +14851,21 @@
         <v>97</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14861,17 +14888,17 @@
         <v>86</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>76</v>
@@ -14920,7 +14947,7 @@
         <v>76</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>85</v>
@@ -14935,21 +14962,21 @@
         <v>97</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14972,17 +14999,17 @@
         <v>76</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>76</v>
@@ -15031,7 +15058,7 @@
         <v>76</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
@@ -15057,10 +15084,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15083,17 +15110,17 @@
         <v>86</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>76</v>
@@ -15142,7 +15169,7 @@
         <v>76</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
@@ -15160,7 +15187,7 @@
         <v>76</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>76</v>
@@ -15168,10 +15195,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15197,13 +15224,13 @@
         <v>309</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15232,10 +15259,10 @@
         <v>150</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>76</v>
@@ -15253,7 +15280,7 @@
         <v>76</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>77</v>
@@ -15268,10 +15295,10 @@
         <v>97</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>76</v>
@@ -15279,10 +15306,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15305,16 +15332,16 @@
         <v>86</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15364,7 +15391,7 @@
         <v>76</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>77</v>
@@ -15379,10 +15406,10 @@
         <v>97</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>76</v>
@@ -15390,10 +15417,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15419,13 +15446,13 @@
         <v>309</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15454,10 +15481,10 @@
         <v>150</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>76</v>
@@ -15475,7 +15502,7 @@
         <v>76</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>77</v>
@@ -15496,15 +15523,15 @@
         <v>76</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15610,10 +15637,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15721,12 +15748,14 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="C121" s="2"/>
+      <c r="C121" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="D121" t="s" s="2">
         <v>76</v>
       </c>
@@ -15735,32 +15764,28 @@
         <v>77</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>138</v>
+        <v>580</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>325</v>
+        <v>581</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>582</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>76</v>
       </c>
@@ -15796,17 +15821,19 @@
         <v>76</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="AC121" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AD121" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>330</v>
+        <v>112</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>77</v>
@@ -15818,7 +15845,7 @@
         <v>76</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>76</v>
@@ -15827,19 +15854,17 @@
         <v>76</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>331</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C122" t="s" s="2">
-        <v>580</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
         <v>76</v>
       </c>
@@ -15848,7 +15873,7 @@
         <v>77</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>86</v>
@@ -15863,10 +15888,10 @@
         <v>138</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>327</v>
@@ -15909,16 +15934,14 @@
         <v>76</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="AC122" s="2"/>
       <c r="AD122" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AF122" t="s" s="2">
         <v>330</v>
@@ -15945,14 +15968,16 @@
         <v>331</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="C123" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="D123" t="s" s="2">
         <v>76</v>
       </c>
@@ -15964,25 +15989,29 @@
         <v>85</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>100</v>
+        <v>334</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P123" t="s" s="2">
         <v>76</v>
       </c>
@@ -16030,19 +16059,19 @@
         <v>76</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>102</v>
+        <v>330</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>76</v>
@@ -16051,26 +16080,26 @@
         <v>76</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>76</v>
+        <v>331</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>76</v>
@@ -16082,17 +16111,15 @@
         <v>76</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>76</v>
@@ -16129,31 +16156,31 @@
         <v>76</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>76</v>
@@ -16165,48 +16192,46 @@
         <v>76</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>226</v>
+        <v>106</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>227</v>
+        <v>107</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>76</v>
       </c>
@@ -16215,7 +16240,7 @@
         <v>76</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>230</v>
+        <v>76</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>76</v>
@@ -16242,31 +16267,31 @@
         <v>76</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>231</v>
+        <v>112</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>76</v>
@@ -16275,15 +16300,15 @@
         <v>76</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>232</v>
+        <v>76</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16291,7 +16316,7 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>85</v>
@@ -16306,18 +16331,20 @@
         <v>86</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O126" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>76</v>
       </c>
@@ -16326,7 +16353,7 @@
         <v>76</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>76</v>
+        <v>230</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>76</v>
@@ -16365,7 +16392,7 @@
         <v>76</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>77</v>
@@ -16386,15 +16413,15 @@
         <v>76</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16402,7 +16429,7 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>85</v>
@@ -16417,18 +16444,18 @@
         <v>86</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N127" s="2"/>
-      <c r="O127" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>76</v>
       </c>
@@ -16476,7 +16503,7 @@
         <v>76</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>77</v>
@@ -16497,15 +16524,15 @@
         <v>76</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16513,13 +16540,13 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G128" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>76</v>
@@ -16528,17 +16555,17 @@
         <v>86</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>76</v>
@@ -16587,7 +16614,7 @@
         <v>76</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>77</v>
@@ -16608,15 +16635,15 @@
         <v>76</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16639,19 +16666,17 @@
         <v>86</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>256</v>
+        <v>99</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>76</v>
@@ -16700,7 +16725,7 @@
         <v>76</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>77</v>
@@ -16721,15 +16746,15 @@
         <v>76</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16752,19 +16777,19 @@
         <v>86</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>99</v>
+        <v>256</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>353</v>
+        <v>257</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>354</v>
+        <v>258</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>355</v>
+        <v>259</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>356</v>
+        <v>260</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>76</v>
@@ -16813,7 +16838,7 @@
         <v>76</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>357</v>
+        <v>261</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>77</v>
@@ -16834,15 +16859,15 @@
         <v>76</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>358</v>
+        <v>262</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16856,7 +16881,7 @@
         <v>85</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>76</v>
@@ -16865,18 +16890,20 @@
         <v>86</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>309</v>
+        <v>99</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>597</v>
+        <v>353</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>598</v>
+        <v>354</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="O131" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>76</v>
       </c>
@@ -16900,11 +16927,13 @@
         <v>76</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y131" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z131" t="s" s="2">
-        <v>600</v>
+        <v>76</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>76</v>
@@ -16922,7 +16951,7 @@
         <v>76</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>596</v>
+        <v>357</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>77</v>
@@ -16943,15 +16972,15 @@
         <v>76</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>76</v>
+        <v>358</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16962,7 +16991,7 @@
         <v>77</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>86</v>
@@ -16971,10 +17000,10 @@
         <v>76</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>602</v>
+        <v>309</v>
       </c>
       <c r="L132" t="s" s="2">
         <v>603</v>
@@ -17009,13 +17038,11 @@
         <v>76</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>76</v>
+        <v>606</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>76</v>
@@ -17033,13 +17060,13 @@
         <v>76</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>76</v>
@@ -17057,12 +17084,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="133" hidden="true">
+    <row r="133">
       <c r="A133" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17076,7 +17103,7 @@
         <v>78</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>76</v>
@@ -17085,16 +17112,16 @@
         <v>76</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>309</v>
+        <v>608</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17120,13 +17147,13 @@
         <v>76</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>610</v>
+        <v>76</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>611</v>
+        <v>76</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>76</v>
@@ -17144,7 +17171,7 @@
         <v>76</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>77</v>
@@ -17196,18 +17223,18 @@
         <v>76</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L134" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="M134" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="N134" s="2"/>
-      <c r="O134" t="s" s="2">
-        <v>616</v>
-      </c>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>76</v>
       </c>
@@ -17231,13 +17258,13 @@
         <v>76</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>76</v>
+        <v>616</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>76</v>
+        <v>617</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>76</v>
@@ -17281,10 +17308,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17307,16 +17334,18 @@
         <v>76</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>309</v>
+        <v>619</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
+      <c r="O135" t="s" s="2">
+        <v>622</v>
+      </c>
       <c r="P135" t="s" s="2">
         <v>76</v>
       </c>
@@ -17340,13 +17369,13 @@
         <v>76</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>620</v>
+        <v>76</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>621</v>
+        <v>76</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>76</v>
@@ -17364,7 +17393,7 @@
         <v>76</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>77</v>
@@ -17388,12 +17417,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17407,7 +17436,7 @@
         <v>78</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>76</v>
@@ -17416,7 +17445,7 @@
         <v>76</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>623</v>
+        <v>309</v>
       </c>
       <c r="L136" t="s" s="2">
         <v>624</v>
@@ -17449,13 +17478,13 @@
         <v>76</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>76</v>
+        <v>626</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>76</v>
+        <v>627</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>76</v>
@@ -17473,7 +17502,7 @@
         <v>76</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>77</v>
@@ -17488,16 +17517,16 @@
         <v>97</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>626</v>
+        <v>76</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>627</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="137" hidden="true">
+    <row r="137">
       <c r="A137" t="s" s="2">
         <v>628</v>
       </c>
@@ -17516,7 +17545,7 @@
         <v>78</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>76</v>
@@ -17525,13 +17554,13 @@
         <v>76</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>516</v>
+        <v>629</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -17597,21 +17626,21 @@
         <v>97</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>76</v>
+        <v>632</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>76</v>
+        <v>633</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17622,7 +17651,7 @@
         <v>77</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>76</v>
@@ -17634,13 +17663,13 @@
         <v>76</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>99</v>
+        <v>517</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>100</v>
+        <v>635</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>101</v>
+        <v>636</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -17691,19 +17720,19 @@
         <v>76</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>102</v>
+        <v>634</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>76</v>
@@ -17717,21 +17746,21 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>76</v>
@@ -17743,17 +17772,15 @@
         <v>76</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>76</v>
@@ -17802,19 +17829,19 @@
         <v>76</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>76</v>
@@ -17828,14 +17855,14 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>523</v>
+        <v>104</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -17848,26 +17875,24 @@
         <v>76</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K140" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>524</v>
+        <v>106</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>525</v>
+        <v>107</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="O140" t="s" s="2">
-        <v>266</v>
-      </c>
+      <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>76</v>
       </c>
@@ -17915,7 +17940,7 @@
         <v>76</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>526</v>
+        <v>112</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>77</v>
@@ -17941,42 +17966,46 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>76</v>
+        <v>524</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I141" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>309</v>
+        <v>105</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>635</v>
+        <v>525</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
+        <v>526</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>76</v>
       </c>
@@ -18000,13 +18029,13 @@
         <v>76</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>164</v>
+        <v>76</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>637</v>
+        <v>76</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>638</v>
+        <v>76</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>76</v>
@@ -18024,19 +18053,19 @@
         <v>76</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>634</v>
+        <v>527</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>76</v>
@@ -18050,10 +18079,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18061,7 +18090,7 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G142" t="s" s="2">
         <v>85</v>
@@ -18076,7 +18105,7 @@
         <v>76</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>640</v>
+        <v>309</v>
       </c>
       <c r="L142" t="s" s="2">
         <v>641</v>
@@ -18109,13 +18138,13 @@
         <v>76</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>76</v>
+        <v>164</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>76</v>
+        <v>643</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>76</v>
+        <v>644</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>76</v>
@@ -18133,10 +18162,10 @@
         <v>76</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>85</v>
@@ -18159,10 +18188,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18170,10 +18199,10 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>76</v>
@@ -18185,20 +18214,16 @@
         <v>76</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="O143" t="s" s="2">
         <v>648</v>
       </c>
+      <c r="N143" s="2"/>
+      <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>76</v>
       </c>
@@ -18246,13 +18271,13 @@
         <v>76</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>76</v>
@@ -18298,18 +18323,20 @@
         <v>76</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>309</v>
+        <v>650</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="O144" s="2"/>
+        <v>653</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>654</v>
+      </c>
       <c r="P144" t="s" s="2">
         <v>76</v>
       </c>
@@ -18333,13 +18360,13 @@
         <v>76</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>652</v>
+        <v>76</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>653</v>
+        <v>76</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>76</v>
@@ -18381,8 +18408,119 @@
         <v>76</v>
       </c>
     </row>
+    <row r="145" hidden="true">
+      <c r="A145" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="O145" s="2"/>
+      <c r="P145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AM144">
+  <autoFilter ref="A1:AM145">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18392,7 +18530,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI143">
+  <conditionalFormatting sqref="A2:AI144">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-lungenfunktion-provokationstest-messung.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-lungenfunktion-provokationstest-messung.xlsx
@@ -1064,7 +1064,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
   &lt;code value="323426006"/&gt;
   &lt;display value="Measurement of respiratory function (procedure)"/&gt;
 &lt;/valueCoding&gt;</t>
@@ -1362,7 +1362,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
   &lt;code value="252520007"/&gt;
   &lt;display value="Methacholine challenge (procedure)"/&gt;
 &lt;/valueCoding&gt;</t>
